--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Obj.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Obj.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -4380,6 +4380,33 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EA 23.283</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>pedra de passagem</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>stepping stone</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>踏み石</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Obj.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Obj.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -4380,33 +4380,6 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>EA 23.283</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>pedra de passagem</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>stepping stone</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>踏み石</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
